--- a/data/trans_bre/P44D-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/P44D-Estudios-trans_bre.xlsx
@@ -606,7 +606,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>-2,08</t>
+          <t>-1,98</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -621,7 +621,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>-67,23%</t>
+          <t>-66,35%</t>
         </is>
       </c>
     </row>
@@ -634,17 +634,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-0,5; 16,39</t>
+          <t>-0,47; 17,42</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-6,69; 4,24</t>
+          <t>-6,65; 4,37</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-5,3; 0,13</t>
+          <t>-5,34; -0,06</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -659,7 +659,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-93,56; 60,94</t>
+          <t>-94,77; 55,16</t>
         </is>
       </c>
     </row>
@@ -686,7 +686,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>2,55</t>
+          <t>-1,57</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -701,7 +701,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>59,48%</t>
+          <t>-18,68%</t>
         </is>
       </c>
     </row>
@@ -714,32 +714,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-15,56; 33,59</t>
+          <t>-15,38; 31,67</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-14,56; 11,95</t>
+          <t>-15,36; 12,87</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-2,16; 7,61</t>
+          <t>-5,42; 2,4</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-70,9; 380,59</t>
+          <t>-71,12; 368,86</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-81,7; 206,02</t>
+          <t>-83,74; 196,86</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-31,83; 453,92</t>
+          <t>-49,63; 41,93</t>
         </is>
       </c>
     </row>
@@ -766,7 +766,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>0,67</t>
+          <t>-0,61</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -781,7 +781,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>3,26%</t>
+          <t>-2,89%</t>
         </is>
       </c>
     </row>
@@ -794,32 +794,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-27,13; 51,84</t>
+          <t>-28,27; 51,51</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-29,3; 35,65</t>
+          <t>-30,65; 33,33</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-9,78; 9,04</t>
+          <t>-9,33; 9,21</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-60,07; 398,11</t>
+          <t>-65,76; 444,96</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-60,97; 132,23</t>
+          <t>-66,74; 130,75</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-35,97; 57,64</t>
+          <t>-36,57; 56,89</t>
         </is>
       </c>
     </row>
@@ -846,7 +846,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>0,68</t>
+          <t>-2,59</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -861,7 +861,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>10,14%</t>
+          <t>-26,29%</t>
         </is>
       </c>
     </row>
@@ -874,32 +874,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-5,81; 16,67</t>
+          <t>-5,06; 15,63</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-12,6; 3,78</t>
+          <t>-13,02; 4,39</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-3,55; 5,76</t>
+          <t>-5,66; 0,19</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-36,74; 220,46</t>
+          <t>-33,03; 194,56</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-69,56; 37,32</t>
+          <t>-69,45; 41,87</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-35,84; 162,1</t>
+          <t>-47,89; 2,61</t>
         </is>
       </c>
     </row>
